--- a/data/kaggle_candidates_v2.xlsx
+++ b/data/kaggle_candidates_v2.xlsx
@@ -15,8 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -76,13 +77,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -448,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:M99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -512,6 +514,11 @@
           <t>reason</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>batch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5014,6 +5021,633 @@
       <c r="L88" t="inlineStr">
         <is>
           <t>Hackathon format, not a standard prediction competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>tabular-playground-series-feb-2022</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Tabular Playground Series - Feb 2022</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>featured</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Categorization Accuracy</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1255</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>44620</v>
+      </c>
+      <c r="G89" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" t="b">
+        <v>1</v>
+      </c>
+      <c r="I89" t="n">
+        <v>2</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/tabular-playground-series-feb-2022</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Expansion batch — TPS 2022 / PS S6 tabular competition</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>tabular-playground-series-mar-2022</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Tabular Playground Series - Mar 2022</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>featured</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Mean Absolute Error</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>956</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>44651</v>
+      </c>
+      <c r="G90" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" t="b">
+        <v>1</v>
+      </c>
+      <c r="I90" t="n">
+        <v>2</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/tabular-playground-series-mar-2022</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Expansion batch — TPS 2022 / PS S6 tabular competition</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>tabular-playground-series-apr-2022</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Tabular Playground Series - Apr 2022</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>featured</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Area Under ROC Curve</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>816</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>44681</v>
+      </c>
+      <c r="G91" t="b">
+        <v>0</v>
+      </c>
+      <c r="H91" t="b">
+        <v>1</v>
+      </c>
+      <c r="I91" t="n">
+        <v>5</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/tabular-playground-series-apr-2022</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Expansion batch — TPS 2022 / PS S6 tabular competition</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>tabular-playground-series-may-2022</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Tabular Playground Series - May 2022</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>featured</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Area Under ROC Curve</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1151</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>44712</v>
+      </c>
+      <c r="G92" t="b">
+        <v>0</v>
+      </c>
+      <c r="H92" t="b">
+        <v>1</v>
+      </c>
+      <c r="I92" t="n">
+        <v>3</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/tabular-playground-series-may-2022</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Expansion batch — TPS 2022 / PS S6 tabular competition</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>tabular-playground-series-jun-2022</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Tabular Playground Series - Jun 2022</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>featured</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Root Mean Squared Error</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>844</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>44742</v>
+      </c>
+      <c r="G93" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" t="b">
+        <v>1</v>
+      </c>
+      <c r="I93" t="n">
+        <v>3</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/tabular-playground-series-jun-2022</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Expansion batch — TPS 2022 / PS S6 tabular competition</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>tabular-playground-series-oct-2022</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Tabular Playground Series - Oct 2022</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>featured</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Mean Columnwise Log Loss</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>463</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>44865</v>
+      </c>
+      <c r="G94" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" t="b">
+        <v>1</v>
+      </c>
+      <c r="I94" t="n">
+        <v>2</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/tabular-playground-series-oct-2022</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Expansion batch — TPS 2022 / PS S6 tabular competition</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>tabular-playground-series-nov-2022</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Tabular Playground Series - Nov 2022</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>featured</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Log Loss</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>689</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>44895</v>
+      </c>
+      <c r="G95" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" t="b">
+        <v>1</v>
+      </c>
+      <c r="I95" t="n">
+        <v>2</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/tabular-playground-series-nov-2022</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Expansion batch — TPS 2022 / PS S6 tabular competition</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>playground-series-s6e1</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Predicting Student Test Scores</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Root Mean Squared Error</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>4317</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>46053</v>
+      </c>
+      <c r="G96" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" t="b">
+        <v>1</v>
+      </c>
+      <c r="I96" t="n">
+        <v>2</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/playground-series-s6e1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Expansion batch — TPS 2022 / PS S6 tabular competition</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>playground-series-s6e2</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Predicting Heart Disease</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Roc Auc Score</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>4370</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>46081</v>
+      </c>
+      <c r="G97" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" t="b">
+        <v>1</v>
+      </c>
+      <c r="I97" t="n">
+        <v>4</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/playground-series-s6e2</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Expansion batch — TPS 2022 / PS S6 tabular competition</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>playground-series-s6e3</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Predict Customer Churn</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Roc Auc Score</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>4142</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>46112</v>
+      </c>
+      <c r="G98" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" t="b">
+        <v>1</v>
+      </c>
+      <c r="I98" t="n">
+        <v>6</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/playground-series-s6e3</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Expansion batch — TPS 2022 / PS S6 tabular competition</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>expansion</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>playground-series-s6e4</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Predicting Irrigation Need</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>playground</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Balanced Accuracy Score</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>4315</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>46142</v>
+      </c>
+      <c r="G99" t="b">
+        <v>0</v>
+      </c>
+      <c r="H99" t="b">
+        <v>1</v>
+      </c>
+      <c r="I99" t="n">
+        <v>4</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>https://www.kaggle.com/competitions/playground-series-s6e4</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>keep</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Expansion batch — TPS 2022 / PS S6 tabular competition</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>expansion</t>
         </is>
       </c>
     </row>
